--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48337-2025 artfynd.xlsx
+++ b/artfynd/A 48337-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001090</v>
       </c>
       <c r="B2" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001089</v>
       </c>
       <c r="B3" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
